--- a/reports/Debug-snowbowl-20251230/For The Week Ending (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20251230/For The Week Ending (Prior Year)_Revenue.xlsx
@@ -474,14 +474,12 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="2">
-        <v>374353.6900</v>
+        <v>-65.7100</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -489,25 +487,27 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="2">
-        <v>16979.1100</v>
+        <v>374353.6900</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="2">
-        <v>-65.7100</v>
+        <v>16979.1100</v>
       </c>
     </row>
     <row r="5" spans="1:4">
